--- a/outputs/daily/hr_rankings_2026-10-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-16.xlsx
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
         <v>41.2</v>
@@ -814,7 +814,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1215,24 +1215,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -1248,11 +1248,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1266,14 +1278,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>43.6</v>
+        <v>53.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
@@ -1282,10 +1294,10 @@
         <v>90.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>54.9</v>
+        <v>34.9</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1294,24 +1306,24 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1324,7 +1336,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1341,12 +1353,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1356,12 +1368,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1371,75 +1383,99 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -1455,12 +1491,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1485,7 +1521,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1504,7 +1540,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.9</v>
+        <v>46.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1518,11 +1554,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>53.3</v>
+        <v>35.1</v>
       </c>
       <c r="Q5" t="n">
         <v>34.3</v>
@@ -1531,13 +1567,13 @@
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>34.9</v>
+        <v>56.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1546,24 +1582,24 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1576,7 +1612,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1593,27 +1629,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1623,67 +1659,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1731,24 +1767,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -1761,26 +1797,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1794,26 +1818,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>35.1</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U6" t="n">
-        <v>56.2</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1822,24 +1846,24 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1852,7 +1876,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1869,27 +1893,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1899,99 +1923,75 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
+          <t>0.2134</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.1</v>
+        <v>38.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
@@ -3154,10 +3154,10 @@
         <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>12</v>
+        <v>36.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3166,24 +3166,24 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3223,17 +3223,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3243,67 +3243,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.08</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3351,24 +3351,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3381,26 +3381,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>35.1</v>
+        <v>35.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3414,26 +3402,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3442,24 +3430,24 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3472,7 +3460,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3489,12 +3477,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3504,12 +3492,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3519,99 +3507,75 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0775</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -3627,24 +3591,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3660,11 +3624,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3678,14 +3654,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>20.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
@@ -3694,10 +3670,10 @@
         <v>59.8</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3706,24 +3682,24 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3736,7 +3712,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3753,27 +3729,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3783,75 +3759,99 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
@@ -3867,24 +3867,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3897,14 +3897,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>33</v>
+        <v>35.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3918,26 +3930,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>43.1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -3946,24 +3958,24 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3976,7 +3988,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -3993,12 +4005,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4008,12 +4020,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4023,75 +4035,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.0775</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -4107,24 +4143,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4137,26 +4173,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>32.5</v>
+        <v>34.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4170,26 +4194,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>13.7</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>32.5</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>72.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4198,24 +4222,24 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4228,7 +4252,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4250,7 +4274,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4265,7 +4289,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4275,99 +4299,75 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -4383,24 +4383,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4413,14 +4413,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4434,26 +4446,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>32.5</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4462,24 +4474,24 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4492,7 +4504,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4509,27 +4521,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4539,75 +4551,99 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -4623,12 +4659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4653,14 +4689,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4678,7 +4714,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>41.2</v>
@@ -4687,13 +4723,13 @@
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
         <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4702,12 +4738,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4749,12 +4785,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4764,7 +4800,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -4779,67 +4815,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr"/>
@@ -4863,24 +4899,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4893,26 +4929,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4926,26 +4950,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U18" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -4954,24 +4978,24 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4984,7 +5008,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5001,12 +5025,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5016,12 +5040,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5031,99 +5055,75 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0707</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
         <v>41.2</v>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -6185,24 +6185,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -6218,11 +6218,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6236,14 +6248,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>43.6</v>
+        <v>53.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
@@ -6252,10 +6264,10 @@
         <v>90.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>54.9</v>
+        <v>34.9</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -6264,24 +6276,24 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -6294,7 +6306,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -6311,12 +6323,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6326,12 +6338,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6341,75 +6353,99 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -6425,12 +6461,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6455,7 +6491,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6474,7 +6510,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.9</v>
+        <v>46.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6488,11 +6524,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>53.3</v>
+        <v>35.1</v>
       </c>
       <c r="Q5" t="n">
         <v>34.3</v>
@@ -6501,13 +6537,13 @@
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>34.9</v>
+        <v>56.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -6516,24 +6552,24 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -6546,7 +6582,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -6563,27 +6599,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -6593,67 +6629,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -6701,24 +6737,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -6731,26 +6767,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6764,26 +6788,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>35.1</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U6" t="n">
-        <v>56.2</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -6792,24 +6816,24 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -6822,7 +6846,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -6839,27 +6863,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6869,99 +6893,75 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
+          <t>0.2134</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.1</v>
+        <v>38.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
@@ -8124,10 +8124,10 @@
         <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>12</v>
+        <v>36.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8136,24 +8136,24 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -8193,17 +8193,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8213,67 +8213,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.08</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8321,24 +8321,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -8351,26 +8351,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>35.1</v>
+        <v>35.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8384,26 +8372,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8412,24 +8400,24 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8442,7 +8430,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8459,12 +8447,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8474,12 +8462,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8489,99 +8477,75 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0775</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -8597,24 +8561,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -8630,11 +8594,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8648,14 +8624,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>20.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
@@ -8664,10 +8640,10 @@
         <v>59.8</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8676,24 +8652,24 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8706,7 +8682,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -8723,27 +8699,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8753,75 +8729,99 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
@@ -8837,24 +8837,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -8867,14 +8867,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>33</v>
+        <v>35.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8888,26 +8900,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>43.1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -8916,24 +8928,24 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8946,7 +8958,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -8963,12 +8975,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -8978,12 +8990,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8993,75 +9005,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.0775</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -9077,24 +9113,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9107,26 +9143,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>32.5</v>
+        <v>34.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9140,26 +9164,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>13.7</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>32.5</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>72.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9168,24 +9192,24 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9198,7 +9222,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9220,7 +9244,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9235,7 +9259,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9245,99 +9269,75 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -9353,24 +9353,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9383,14 +9383,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9404,26 +9416,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>32.5</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9432,24 +9444,24 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9462,7 +9474,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -9479,27 +9491,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9509,75 +9521,99 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -9593,12 +9629,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9623,14 +9659,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9648,7 +9684,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>41.2</v>
@@ -9657,13 +9693,13 @@
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
         <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9672,12 +9708,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -9719,12 +9755,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -9734,7 +9770,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -9749,67 +9785,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr"/>
@@ -9833,24 +9869,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9863,26 +9899,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9896,26 +9920,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U18" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -9924,24 +9948,24 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9954,7 +9978,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -9971,12 +9995,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -9986,12 +10010,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10001,99 +10025,75 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0707</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-16.xlsx
@@ -768,11 +768,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>51.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -793,7 +805,7 @@
         <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
@@ -802,7 +814,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
@@ -844,7 +856,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -881,7 +893,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -954,12 +966,36 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -1008,11 +1044,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1026,14 +1074,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
@@ -1042,7 +1090,7 @@
         <v>95.5</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
         <v>28.9</v>
@@ -1084,7 +1132,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1121,7 +1169,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1194,12 +1242,36 @@
           <t>0.1639</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -1800,11 +1872,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1818,14 +1902,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
@@ -1834,7 +1918,7 @@
         <v>71.7</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
         <v>54.9</v>
@@ -1876,7 +1960,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1913,7 +1997,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1986,12 +2070,36 @@
           <t>0.2134</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -2007,24 +2115,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -2037,14 +2145,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>43.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2058,26 +2178,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2091,7 +2211,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2116,7 +2236,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2133,12 +2253,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2148,12 +2268,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2163,75 +2283,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -2247,24 +2391,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -2277,17 +2421,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2296,7 +2440,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2310,26 +2454,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2343,7 +2487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2385,12 +2529,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2400,12 +2544,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2415,97 +2559,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
@@ -3351,24 +3495,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3381,14 +3525,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3402,26 +3558,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3435,7 +3591,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3460,7 +3616,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3477,12 +3633,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3492,12 +3648,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3507,75 +3663,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -3591,24 +3771,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3621,17 +3801,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3640,7 +3820,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3654,26 +3834,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>20.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3687,7 +3867,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3712,7 +3892,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3729,12 +3909,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3744,12 +3924,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3759,97 +3939,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -4143,24 +4323,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4173,14 +4353,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4194,26 +4386,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4227,7 +4419,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4252,7 +4444,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4274,7 +4466,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4289,7 +4481,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4299,75 +4491,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -4383,24 +4599,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4413,17 +4629,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4432,7 +4648,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4446,26 +4662,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4479,7 +4695,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4521,27 +4737,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4551,97 +4767,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -4659,12 +4875,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4689,14 +4905,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>32.2</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4710,26 +4938,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4743,7 +4971,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4768,7 +4996,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4785,27 +5013,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4815,75 +5043,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -4932,11 +5184,23 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4950,14 +5214,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
@@ -4966,7 +5230,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
         <v>15.3</v>
@@ -5008,7 +5272,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5045,7 +5309,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5118,12 +5382,36 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -5172,11 +5460,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5197,7 +5497,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -5248,7 +5548,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5285,7 +5585,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5358,12 +5658,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
@@ -5738,11 +6062,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>51.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5763,7 +6099,7 @@
         <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
@@ -5772,7 +6108,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
@@ -5814,7 +6150,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5851,7 +6187,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -5924,12 +6260,36 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -5978,11 +6338,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5996,14 +6368,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
@@ -6012,7 +6384,7 @@
         <v>95.5</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
         <v>28.9</v>
@@ -6054,7 +6426,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -6091,7 +6463,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -6164,12 +6536,36 @@
           <t>0.1639</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -6770,11 +7166,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6788,14 +7196,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
@@ -6804,7 +7212,7 @@
         <v>71.7</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
         <v>54.9</v>
@@ -6846,7 +7254,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -6883,7 +7291,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6956,12 +7364,36 @@
           <t>0.2134</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -6977,24 +7409,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -7007,14 +7439,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>43.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7028,26 +7472,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7061,7 +7505,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7086,7 +7530,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7103,12 +7547,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7118,12 +7562,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7133,75 +7577,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -7217,24 +7685,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -7247,17 +7715,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7266,7 +7734,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7280,26 +7748,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7313,7 +7781,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7355,12 +7823,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7370,12 +7838,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7385,97 +7853,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
@@ -8321,24 +8789,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -8351,14 +8819,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8372,26 +8852,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8405,7 +8885,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -8430,7 +8910,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8447,12 +8927,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8462,12 +8942,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8477,75 +8957,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -8561,24 +9065,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -8591,17 +9095,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -8610,7 +9114,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8624,26 +9128,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>20.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8657,7 +9161,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -8682,7 +9186,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -8699,12 +9203,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -8714,12 +9218,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8729,97 +9233,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -9113,24 +9617,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9143,14 +9647,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9164,26 +9680,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9197,7 +9713,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9222,7 +9738,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9244,7 +9760,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9259,7 +9775,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9269,75 +9785,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -9353,24 +9893,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9383,17 +9923,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9402,7 +9942,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9416,26 +9956,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9449,7 +9989,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -9491,27 +10031,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9521,97 +10061,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -9629,12 +10169,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9659,14 +10199,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>32.2</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9680,26 +10232,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9713,7 +10265,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -9738,7 +10290,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9755,27 +10307,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9785,75 +10337,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -9902,11 +10478,23 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9920,14 +10508,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
@@ -9936,7 +10524,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
         <v>15.3</v>
@@ -9978,7 +10566,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10015,7 +10603,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10088,12 +10676,36 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -10142,11 +10754,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10167,7 +10791,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -10218,7 +10842,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -10255,7 +10879,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10328,12 +10952,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
